--- a/docs/Test_Report/Port/TestPlanExecutionReport_Port.xlsx
+++ b/docs/Test_Report/Port/TestPlanExecutionReport_Port.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Template Revision History" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="000000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -131,10 +136,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -716,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593,MCAL-29598</t>
+          <t>MCAL-30786,MCAL-30788</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -726,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13 23:19:48.569014-05:00 CDT</t>
+          <t>2025-06-09 06:41:22.826925-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -798,32 +806,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -835,12 +843,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -872,12 +880,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1020,32 +1028,32 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1119,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1143,12 +1151,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1175,12 +1183,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1306,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1354,7 +1362,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -1373,24 +1381,37 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>60</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
     </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1401,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1537,12 +1558,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1649,12 +1670,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1668,12 +1689,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1780,12 +1801,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1799,12 +1820,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1911,12 +1932,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1930,12 +1951,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2042,12 +2063,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2061,12 +2082,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2173,12 +2194,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2192,12 +2213,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2304,12 +2325,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2323,12 +2344,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2435,12 +2456,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2454,12 +2475,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2566,12 +2587,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2585,12 +2606,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2698,12 +2719,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2717,12 +2738,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2829,12 +2850,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2848,12 +2869,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2960,12 +2981,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2979,12 +3000,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3091,12 +3112,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3110,12 +3131,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3222,12 +3243,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3241,12 +3262,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3356,12 +3377,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3375,12 +3396,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3490,12 +3511,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3509,12 +3530,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3624,12 +3645,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3643,12 +3664,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3758,12 +3779,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3777,12 +3798,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3890,12 +3911,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3909,12 +3930,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4024,12 +4045,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4043,12 +4064,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4155,12 +4176,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4174,12 +4195,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4286,12 +4307,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4305,12 +4326,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4421,12 +4442,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4440,12 +4461,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4555,12 +4576,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4574,12 +4595,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4690,12 +4711,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4709,12 +4730,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4824,12 +4845,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4843,12 +4864,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4955,12 +4976,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4974,12 +4995,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5086,12 +5107,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5105,12 +5126,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5217,12 +5238,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5236,12 +5257,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5348,12 +5369,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5367,12 +5388,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5479,12 +5500,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5498,12 +5519,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5610,12 +5631,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5629,12 +5650,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5742,12 +5763,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5761,12 +5782,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5874,12 +5895,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5893,12 +5914,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -6008,12 +6029,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6027,12 +6048,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6052,7 +6073,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29443,MCAL-29441,MCAL-29440,MCAL-29442,MCAL-22340,MCAL-22321,MCAL-22335,MCAL-22336,MCAL-22322,MCAL-22323,MCAL-22341,MCAL-22343,MCAL-22344,MCAL-22349,MCAL-22351,MCAL-22353,MCAL-23517,MCAL-22383,MCAL-22386,MCAL-23519,MCAL-22339,MCAL-22398,MCAL-22409,MCAL-23520,MCAL-22347,MCAL-22411,MCAL-22392,MCAL-22402,MCAL-22342,MCAL-22352,MCAL-22313,MCAL-22317,MCAL-22389,MCAL-22387,MCAL-22390,MCAL-22412,MCAL-22703,MCAL-22330,MCAL-22334,MCAL-22337,MCAL-22338,MCAL-22391,MCAL-22393,MCAL-22394,MCAL-22396,MCAL-22325,MCAL-22397,MCAL-22403,MCAL-22345,MCAL-22346</t>
+          <t>MCAL-29443,MCAL-29441,MCAL-29440,MCAL-29442,MCAL-22340,MCAL-22331,MCAL-22321,MCAL-22335,MCAL-22336,MCAL-22322,MCAL-22323,MCAL-22341,MCAL-22343,MCAL-22344,MCAL-22349,MCAL-22351,MCAL-22353,MCAL-23517,MCAL-22383,MCAL-22386,MCAL-23519,MCAL-22339,MCAL-22398,MCAL-22409,MCAL-23520,MCAL-22347,MCAL-22411,MCAL-22392,MCAL-22402,MCAL-22342,MCAL-22352,MCAL-22313,MCAL-22317,MCAL-22389,MCAL-22387,MCAL-22390,MCAL-22412,MCAL-22703,MCAL-22330,MCAL-22334,MCAL-22337,MCAL-22338,MCAL-22391,MCAL-22393,MCAL-22394,MCAL-22396,MCAL-22325,MCAL-22397,MCAL-22403,MCAL-22345</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -6139,12 +6160,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6158,12 +6179,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6270,12 +6291,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6289,12 +6310,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6401,12 +6422,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6420,12 +6441,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6535,12 +6556,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6554,12 +6575,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6666,12 +6687,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6685,12 +6706,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29599</t>
+          <t>MCAL-30785</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6797,12 +6818,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29593</t>
+          <t>MCAL-30786</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Automated Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Automated Test Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6816,12 +6837,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6896,31 +6917,31 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U42" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7027,31 +7048,31 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7158,31 +7179,31 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
-      <c r="U44" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7289,31 +7310,31 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
       <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7420,31 +7441,31 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7551,31 +7572,31 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
       <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7650,31 +7671,31 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
       <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7694,7 +7715,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-12326,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425,MCAL-12447,MCAL-12438,MCAL-12444,MCAL-12357,MCAL-12330</t>
+          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12445,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12366,MCAL-12306,MCAL-12360,MCAL-12396,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-12326,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -7749,31 +7770,31 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
       <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U49" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -7848,31 +7869,31 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
       <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -7948,31 +7969,31 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
       <c r="T51" s="3" t="inlineStr"/>
-      <c r="U51" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -8048,31 +8069,31 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
       <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -8147,31 +8168,31 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
       <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8246,31 +8267,31 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
       <c r="T54" s="3" t="inlineStr"/>
-      <c r="U54" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -8345,31 +8366,31 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
       <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U55" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8444,31 +8465,31 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
       <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U56" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8544,31 +8565,31 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
       <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U57" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -8643,31 +8664,31 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
       <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U58" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -8742,31 +8763,31 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
       <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U59" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -8844,31 +8865,31 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
       <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U60" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29600</t>
+          <t>MCAL-30787</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -8943,24 +8964,123 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29598</t>
+          <t>MCAL-30788</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : PORT - Manual Test Run</t>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
       <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="10" t="inlineStr">
+      <c r="U61" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30787</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30796</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Manual test case to verify the configurability of Port pins in different pin packages</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-22408</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm,F29P58x-evm</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>{color:#172b4d}Manual test case to verify the configurability of Port pins in different pin packages{color}</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>No errors observed in Eb tresos configurator</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30788</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : PORT - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U61"/>
+  <autoFilter ref="A1:U62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9009,12 +9129,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Test Plan</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Test Plan Key</t>
         </is>
@@ -9036,8 +9156,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Test Plan Name</t>
         </is>
@@ -9059,8 +9179,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="A4" s="12" t="n"/>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Test Case Key</t>
         </is>
@@ -9082,8 +9202,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
@@ -9105,8 +9225,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="A6" s="12" t="n"/>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Associated Issue(s) Type</t>
         </is>
@@ -9133,8 +9253,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Associated Issue(s) ID(s)</t>
         </is>
@@ -9156,8 +9276,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Test Platform</t>
         </is>
@@ -9179,8 +9299,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Test Level</t>
         </is>
@@ -9196,7 +9316,7 @@
 -- "Not Provided" if no 'Test Scope' is provided in Jira</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9208,8 +9328,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
@@ -9231,8 +9351,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Test Setup</t>
         </is>
@@ -9254,8 +9374,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Pass/Fail Criteria</t>
         </is>
@@ -9277,8 +9397,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
@@ -9289,7 +9409,7 @@
 (Map Test Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9301,15 +9421,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="12" t="n"/>
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="13" t="n"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Functional:
 Tests covering functional requirements-based  aspects of the software</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9321,8 +9441,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="12" t="n"/>
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="13" t="n"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Compatability:
@@ -9330,7 +9450,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing that measures the degree to which a test item can function satisfactorily alongside other independent products in a shared environment (co-existence), and where necessary, exchanges information with other systems or components (interoperability)</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9342,15 +9462,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="12" t="n"/>
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="13" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Usability:
 Test Case covers usability/api/look and feel aspects of the module including out-of box (OOB) experience</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9362,15 +9482,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="12" t="n"/>
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="13" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Fault Injection:
 Testing based on injection of errors or faults to ensure no unintended consequences</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9382,8 +9502,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="12" t="n"/>
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="13" t="n"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Performance: 
@@ -9391,7 +9511,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item accomplishes its designated functions within given constraints of time and other resources</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9403,8 +9523,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="12" t="n"/>
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="13" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Reliability: 
@@ -9412,7 +9532,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ability of a test item to perform its required functions, including evaluating the frequency with which failures occur, when it is used under stated conditions for a specified period of time</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9424,8 +9544,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="12" t="n"/>
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="13" t="n"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Stress:
@@ -9433,7 +9553,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of performance efficiency testing conducted to evaluate a test item's behaviour under conditions of loading above anticipated or specified capacity requirements, or of resource availability below minimum specified requirements</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9445,8 +9565,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="12" t="n"/>
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="13" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Security:
@@ -9454,7 +9574,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item, and associated data and information, are protected so that unauthorized persons or systems cannot use, read, or modify them, and authorized persons or systems are not denied access to them</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9466,8 +9586,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="12" t="n"/>
+      <c r="A22" s="12" t="n"/>
+      <c r="B22" s="13" t="n"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Maintainability:
@@ -9475,7 +9595,7 @@
 ISO/IEC/IEEE 29119-1 Defn: test type conducted to evaluate the degree of effectiveness and efficiency with which a test item may be modified</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9487,8 +9607,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="12" t="n"/>
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="13" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Portability:
@@ -9496,7 +9616,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ease with which a test item can be transferred from one hardware or software environment to another, including the level of modification needed for it to be executed in various types of environment</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9508,8 +9628,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Test Design Technique</t>
         </is>
@@ -9521,7 +9641,7 @@
 (Map Test Derivation Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9533,8 +9653,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="12" t="n"/>
+      <c r="A25" s="12" t="n"/>
+      <c r="B25" s="13" t="n"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Requirements-Analysis:
@@ -9542,7 +9662,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9554,15 +9674,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="12" t="n"/>
+      <c r="A26" s="12" t="n"/>
+      <c r="B26" s="13" t="n"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Boundary Value Analysis:
 Test cases that apply to interfaces and values approaching and crossing the boundaries and out of range values</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9574,15 +9694,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="12" t="n"/>
+      <c r="A27" s="12" t="n"/>
+      <c r="B27" s="13" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Error Guessing:
 Test cases established based on lessons learned and expert judgement to determine situations that may cause software failures or errors to appear</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9594,28 +9714,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="12" t="n"/>
+      <c r="A28" s="12" t="n"/>
+      <c r="B28" s="13" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Other (Use case analysis; Customer Usage; Requirement analysis; Failure Mode analysis):
 Teams are encouraged to use techniques defined by standards such as ISO/IEC/IEEE 29119-4; which needs to be refelcted within Qmetry</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="A29" s="12" t="n"/>
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Test Execution Type</t>
         </is>
@@ -9625,7 +9745,7 @@
           <t>Identifies whether the case is automated or manually or Semi-Automated executed</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9637,8 +9757,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="A30" s="12" t="n"/>
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Test Category</t>
         </is>
@@ -9648,7 +9768,7 @@
           <t>Test Categories represent sets of tests that are commonly used.</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9660,15 +9780,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="12" t="n"/>
+      <c r="A31" s="12" t="n"/>
+      <c r="B31" s="13" t="n"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Sanity:
 This Test case is identified to run for Sanity Checks. These are mainly the basic tests that need to be run as part of entry to validate phase</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9680,15 +9800,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="12" t="n"/>
+      <c r="A32" s="12" t="n"/>
+      <c r="B32" s="13" t="n"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Full:
 This category means running all test cases for identified releases</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9700,15 +9820,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="12" t="n"/>
+      <c r="A33" s="12" t="n"/>
+      <c r="B33" s="13" t="n"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Base Regression:
 This Test case is identified to run for the Base Regression / maintenance releases</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -9720,8 +9840,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Test Component(s)</t>
         </is>
@@ -9731,24 +9851,24 @@
           <t xml:space="preserve">The field provides the Component(s) (in Jira) to which the Test Case is mapped to. </t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Test Execution</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Build/Release Key</t>
         </is>
@@ -9770,8 +9890,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="n"/>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Defect Key</t>
         </is>
@@ -9793,8 +9913,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n"/>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>Defect Summary</t>
         </is>
@@ -9816,8 +9936,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="n"/>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
@@ -9840,8 +9960,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="n"/>
-      <c r="B39" s="12" t="n"/>
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="13" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
           <t>PASS
@@ -9860,8 +9980,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="n"/>
-      <c r="B40" s="12" t="n"/>
+      <c r="A40" s="14" t="n"/>
+      <c r="B40" s="13" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
           <t>FAIL
@@ -9880,8 +10000,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="n"/>
-      <c r="B41" s="12" t="n"/>
+      <c r="A41" s="14" t="n"/>
+      <c r="B41" s="13" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
           <t>BLOCKED
@@ -9900,8 +10020,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n"/>
-      <c r="B42" s="12" t="n"/>
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="13" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>WIP
